--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ItemProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemProto!$S$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemProto!$R$1:$R$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -212,1643 +212,10 @@
           <t xml:space="preserve">：宝石
 </t>
         </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>5</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">：宠物之核
-</t>
-        </r>
       </text>
     </comment>
     <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>当道具类型为</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">（消耗品）时该字段的意义
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">获得金币值
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">获得经验值
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">4 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">回城卷轴
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">5 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">图纸制造
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">6 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">随机宝箱
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">8 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">碎片兑换
-9 充值达到一定额度开启宝箱获得道具
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">12 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">清空bossCD
-14 召唤怪物战斗
-15 附魔类道具
-16 学习制造
-17 增幅类道具
-18 晶核道具
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">101 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>触发某个技能</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">ID
-102 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>宠物蛋</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>需要去宠物蛋</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>NPC</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>里孵化</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">)
-103 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>宠物蛋</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>点击使用直接获得</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>个宠物</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-104 随机道具盒子
-105 宠物洗炼相关道具
-106 道具盒子,打开获取指定东西
-107 使用永久获得对应的技能ID
-108 宠物增加经验,跟等级系数相关
-109 宠物增加等级,等级直接+1级,当前经验保留
-110 领主怪物召唤
-111 金币袋子
-112 经验木桩
-113 藏宝图
-114 宝石
-115 宠物皮肤激活道具
-116 角色洗点
-117 宠物洗点
-118 宠物资质
-119 宠物成长
-120 充值积分
-121 鉴定装备卷轴
-122 宠物技能石
-123 宠物扩展工具
-124 仓库扩展工具
-125 宠物坐骑激活道具
-126 集字
-127 藏宝图(随机抽奖)
-128 称号
-129 激活精灵
-130 背包扩展道具
-131 烹饪道具
-132 赛季果实
-133 变异宠物洗练属性道具
-134 普通宠物变成变异
-135 变身道具
-136 宠物技能锁定
-137 加强孵化宠物蛋
-138 增加副本次数
-139 增加背包格子
-140 增加仓库格子
-2 材料
-1 默认其他
-101 拍卖行出售列表可以搜到
-105 刷新宠物资质和技能
-121 鉴定符
-122 宠物技能书
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>当道具类型为</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">（装备）时该字段的意义
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">武器
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">衣服
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">3 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">护符
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">4 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">戒指
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">5 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">饰品
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">6 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">鞋子
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">7 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">裤子
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">8 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">腰带
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">9 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">手镯
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">10 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">头盔
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">11 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">项链
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1101 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">子·鼠
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1102 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">丑·牛
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1103 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">寅·虎
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1104 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">卯·兔
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1105 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">辰·龙
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1106 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">巳·蛇
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1107 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">午·马
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1108 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">未·羊
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1109 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">申·猴
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1110 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">酉·鸡
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1111 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">戌·狗
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1112 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">亥·猪
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1201 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>子·鼠</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1202 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>丑·牛</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1203 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>寅·虎</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1204 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>卯·兔</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1205 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>辰·龙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1206 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>巳·蛇</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1207 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>午·马</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1208 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>未·羊</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1209 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>申·猴</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1210 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>酉·鸡</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1211 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>戌·狗</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1212 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>亥·猪</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1301 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>子·鼠</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1302 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>丑·牛</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1303 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>寅·虎</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1304 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>卯·兔</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1305 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>辰·龙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1306 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>巳·蛇</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1307 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>午·马</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1308 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>未·羊</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1309 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>申·猴</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1310 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>酉·鸡</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1311 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>戌·狗</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">级
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1312 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>亥·猪</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>级
-晶核装备
-当该字段为宝石时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">:
-101 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>黄色孔位
-102 紫色孔位
-103 蓝色孔位
-104 绿色孔位
-110 任意孔位  不可卸载
-111 任意孔位  可以卸载
-当该字段为宠物之核时:
-1:进攻能量
-2:守护能量
-3:生命能量
-宠物装备
-3001 项圈
-3002 铠甲
-3003 护腕</t>
-        </r>
-      </text>
+      <text/>
     </comment>
     <comment ref="L3" authorId="0">
       <text>
@@ -1915,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1952,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1975,7 +342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1999,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2023,7 +390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0">
+    <comment ref="Y3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2046,7 +413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="0">
+    <comment ref="Z3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2075,7 +442,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -2122,9 +489,6 @@
     <t>装备ID</t>
   </si>
   <si>
-    <t>宠物之核合成新道具</t>
-  </si>
-  <si>
     <t xml:space="preserve">道具使用参数 </t>
   </si>
   <si>
@@ -2132,9 +496,6 @@
   </si>
   <si>
     <t>道具Tips显示技能</t>
-  </si>
-  <si>
-    <t>洗练石数量</t>
   </si>
   <si>
     <t>回收获取物品</t>
@@ -2197,9 +558,6 @@
     <t>ItemEquipID</t>
   </si>
   <si>
-    <t>PetHeXinHeChengID</t>
-  </si>
-  <si>
     <t>ItemUsePar</t>
   </si>
   <si>
@@ -2224,9 +582,6 @@
       </rPr>
       <t>killIDIfShow</t>
     </r>
-  </si>
-  <si>
-    <t>XiLianStone</t>
   </si>
   <si>
     <t>HuiShouGetItem</t>
@@ -2256,16 +611,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>（测试）元宝</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>1000018,0</t>
   </si>
   <si>
     <t>可以在商人购买商品时使用的货币。</t>
@@ -2308,9 +657,6 @@
   </si>
   <si>
     <t>（测试）坚壁刀</t>
-  </si>
-  <si>
-    <t>1000018,5</t>
   </si>
   <si>
     <t>1000019,8</t>
@@ -2562,14 +908,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -9304,7 +7650,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{4DE8D1EC-6990-485D-A7F3-BE1006426381}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{29C623DD-F4B2-4465-9227-8CA2C6ACDD18}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -9604,7 +7950,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AB15"/>
+  <dimension ref="C1:Z15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
@@ -9614,28 +7960,26 @@
     <col min="6" max="9" width="17.875" customWidth="1"/>
     <col min="10" max="10" width="11.625" customWidth="1"/>
     <col min="11" max="11" width="21.5" customWidth="1"/>
-    <col min="12" max="12" width="21.875" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
+    <col min="12" max="12" width="22.75" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
     <col min="14" max="14" width="16.125" customWidth="1"/>
     <col min="15" max="15" width="9.625" customWidth="1"/>
     <col min="16" max="16" width="15.5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
-    <col min="18" max="18" width="39.625" customWidth="1"/>
-    <col min="19" max="19" width="45.375" customWidth="1"/>
-    <col min="20" max="20" width="25.75" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="22" width="33.75" customWidth="1"/>
-    <col min="23" max="23" width="79.875" customWidth="1"/>
-    <col min="24" max="24" width="43.125" customWidth="1"/>
-    <col min="25" max="28" width="15" customWidth="1"/>
+    <col min="17" max="17" width="39.625" customWidth="1"/>
+    <col min="18" max="18" width="45.375" customWidth="1"/>
+    <col min="19" max="19" width="25.75" customWidth="1"/>
+    <col min="20" max="20" width="33.75" customWidth="1"/>
+    <col min="21" max="21" width="79.875" customWidth="1"/>
+    <col min="22" max="22" width="43.125" customWidth="1"/>
+    <col min="23" max="26" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="3:28">
+    <row r="1" s="1" customFormat="1" spans="3:26">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:28">
+    <row r="3" ht="20.1" customHeight="1" spans="3:26">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -9693,10 +8037,10 @@
       <c r="U3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="X3" s="5" t="s">
@@ -9708,182 +8052,164 @@
       <c r="Z3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:28">
+    <row r="4" ht="20.1" customHeight="1" spans="3:26">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="5" t="s">
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AA4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>51</v>
+      <c r="E5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:28">
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:28">
+    <row r="6" ht="20.1" customHeight="1" spans="3:26">
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -9918,45 +8244,41 @@
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
       <c r="R6" s="8">
         <v>0</v>
       </c>
       <c r="S6" s="8">
         <v>0</v>
       </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V6" s="11"/>
-      <c r="W6" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="X6" s="13" t="s">
-        <v>59</v>
+      <c r="T6" s="11"/>
+      <c r="U6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="V6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="W6" s="8">
+        <v>0</v>
+      </c>
+      <c r="X6" s="8">
+        <v>1</v>
       </c>
       <c r="Y6" s="8">
         <v>0</v>
       </c>
       <c r="Z6" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:28">
+    <row r="7" ht="20.1" customHeight="1" spans="3:26">
       <c r="C7" s="7">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E7" s="8">
         <v>2</v>
@@ -9994,54 +8316,50 @@
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
       <c r="R7" s="8">
         <v>0</v>
       </c>
       <c r="S7" s="8">
         <v>0</v>
       </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" s="11"/>
-      <c r="W7" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="X7" s="13" t="s">
-        <v>62</v>
+      <c r="T7" s="11"/>
+      <c r="U7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" s="8">
+        <v>0</v>
+      </c>
+      <c r="X7" s="8">
+        <v>1</v>
       </c>
       <c r="Y7" s="8">
         <v>0</v>
       </c>
       <c r="Z7" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:28">
+    <row r="8" ht="20.1" customHeight="1" spans="3:26">
       <c r="C8" s="7">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -10070,43 +8388,39 @@
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="8"/>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
       <c r="R8" s="8">
         <v>0</v>
       </c>
       <c r="S8" s="8">
         <v>0</v>
       </c>
-      <c r="T8" s="8">
-        <v>0</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V8" s="11"/>
-      <c r="W8" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="X8" s="13"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="V8" s="13"/>
+      <c r="W8" s="8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="8">
+        <v>1</v>
+      </c>
       <c r="Y8" s="8">
         <v>0</v>
       </c>
       <c r="Z8" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:28">
+    <row r="9" ht="20.1" customHeight="1" spans="3:26">
       <c r="C9" s="7">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E9" s="8">
         <v>4</v>
@@ -10115,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
@@ -10144,43 +8458,39 @@
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
       <c r="R9" s="8">
         <v>0</v>
       </c>
       <c r="S9" s="8">
         <v>0</v>
       </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V9" s="11"/>
-      <c r="W9" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="X9" s="13"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="V9" s="13"/>
+      <c r="W9" s="8">
+        <v>0</v>
+      </c>
+      <c r="X9" s="8">
+        <v>1</v>
+      </c>
       <c r="Y9" s="8">
         <v>0</v>
       </c>
       <c r="Z9" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:28">
+    <row r="10" ht="20.1" customHeight="1" spans="3:26">
       <c r="C10" s="7">
         <v>5</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E10" s="8">
         <v>5</v>
@@ -10189,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H10" s="8">
         <v>0</v>
@@ -10218,43 +8528,39 @@
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="8"/>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
       <c r="R10" s="8">
         <v>0</v>
       </c>
       <c r="S10" s="8">
         <v>0</v>
       </c>
-      <c r="T10" s="8">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V10" s="11"/>
-      <c r="W10" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="X10" s="13"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="V10" s="13"/>
+      <c r="W10" s="8">
+        <v>0</v>
+      </c>
+      <c r="X10" s="8">
+        <v>1</v>
+      </c>
       <c r="Y10" s="8">
         <v>0</v>
       </c>
       <c r="Z10" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C11" s="7">
         <v>6</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E11" s="14">
         <v>10000101</v>
@@ -10294,37 +8600,33 @@
       </c>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17">
-        <v>0</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V11" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W11" s="19"/>
-      <c r="X11" s="20"/>
+      <c r="S11" s="17">
+        <v>0</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="U11" s="19"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="17">
+        <v>0</v>
+      </c>
+      <c r="X11" s="17">
+        <v>0</v>
+      </c>
       <c r="Y11" s="17">
         <v>0</v>
       </c>
       <c r="Z11" s="17">
         <v>0</v>
       </c>
-      <c r="AA11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C12" s="7">
         <v>7</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E12" s="14">
         <v>10000101</v>
@@ -10364,37 +8666,33 @@
       </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="W12" s="19"/>
-      <c r="X12" s="20"/>
+      <c r="S12" s="17">
+        <v>0</v>
+      </c>
+      <c r="T12" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="U12" s="19"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="17">
+        <v>0</v>
+      </c>
+      <c r="X12" s="17">
+        <v>0</v>
+      </c>
       <c r="Y12" s="17">
         <v>0</v>
       </c>
       <c r="Z12" s="17">
         <v>0</v>
       </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C13" s="7">
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E13" s="14">
         <v>10000101</v>
@@ -10434,37 +8732,33 @@
       </c>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17">
-        <v>0</v>
-      </c>
-      <c r="U13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="W13" s="19"/>
-      <c r="X13" s="20"/>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="U13" s="19"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
       <c r="Y13" s="17">
         <v>0</v>
       </c>
       <c r="Z13" s="17">
         <v>0</v>
       </c>
-      <c r="AA13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C14" s="7">
         <v>9</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E14" s="14">
         <v>10000101</v>
@@ -10504,37 +8798,33 @@
       </c>
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17">
-        <v>0</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V14" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="W14" s="19"/>
-      <c r="X14" s="20"/>
+      <c r="S14" s="17">
+        <v>0</v>
+      </c>
+      <c r="T14" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="U14" s="19"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="17">
+        <v>0</v>
+      </c>
+      <c r="X14" s="17">
+        <v>0</v>
+      </c>
       <c r="Y14" s="17">
         <v>0</v>
       </c>
       <c r="Z14" s="17">
         <v>0</v>
       </c>
-      <c r="AA14" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C15" s="7">
         <v>10</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E15" s="14">
         <v>10000101</v>
@@ -10572,37 +8862,33 @@
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17">
+      <c r="Q15" s="17">
         <v>2000</v>
       </c>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V15" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="W15" s="19"/>
-      <c r="X15" s="20"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17">
+        <v>0</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="U15" s="19"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="17">
+        <v>0</v>
+      </c>
+      <c r="X15" s="17">
+        <v>0</v>
+      </c>
       <c r="Y15" s="17">
         <v>0</v>
       </c>
       <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="S1:S15" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="R1:R15" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
